--- a/NTu/Kabianga_Napier_results.xlsx
+++ b/NTu/Kabianga_Napier_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>101.8064477540805</v>
+        <v>106.3528863367183</v>
       </c>
       <c r="C3" t="n">
         <v>113.651515440767</v>
       </c>
       <c r="D3" t="n">
-        <v>11.84506768668648</v>
+        <v>7.298629104048686</v>
       </c>
       <c r="E3" t="n">
-        <v>11.84536688256107</v>
+        <v>7.298928299923276</v>
       </c>
       <c r="F3" t="n">
-        <v>43.43301190272391</v>
+        <v>26.76273709971868</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>95.59338068013541</v>
+        <v>102.532454813044</v>
       </c>
       <c r="C4" t="n">
         <v>113.6515146554438</v>
       </c>
       <c r="D4" t="n">
-        <v>18.05813397530844</v>
+        <v>11.11905984239982</v>
       </c>
       <c r="E4" t="n">
-        <v>6.21306628862196</v>
+        <v>3.820430738351135</v>
       </c>
       <c r="F4" t="n">
-        <v>22.78124305828052</v>
+        <v>14.00824604062083</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>91.70957226174193</v>
+        <v>100.1565007027278</v>
       </c>
       <c r="C5" t="n">
         <v>113.6515139402186</v>
       </c>
       <c r="D5" t="n">
-        <v>21.94194167847668</v>
+        <v>13.49501323749084</v>
       </c>
       <c r="E5" t="n">
-        <v>3.883807703168245</v>
+        <v>2.375953395091017</v>
       </c>
       <c r="F5" t="n">
-        <v>14.24062824495023</v>
+        <v>8.711829115333728</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>89.07737619952675</v>
+        <v>98.5608561795971</v>
       </c>
       <c r="C6" t="n">
         <v>113.6515132888343</v>
       </c>
       <c r="D6" t="n">
-        <v>24.57413708930757</v>
+        <v>15.09065710923723</v>
       </c>
       <c r="E6" t="n">
-        <v>2.632195410830889</v>
+        <v>1.59564387174639</v>
       </c>
       <c r="F6" t="n">
-        <v>9.651383173046591</v>
+        <v>5.850694196403428</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>87.13786060904333</v>
+        <v>97.40026640827067</v>
       </c>
       <c r="C7" t="n">
         <v>113.6515126955925</v>
       </c>
       <c r="D7" t="n">
-        <v>26.5136520865492</v>
+        <v>16.25124628732186</v>
       </c>
       <c r="E7" t="n">
-        <v>1.939514997241631</v>
+        <v>1.160589178084635</v>
       </c>
       <c r="F7" t="n">
-        <v>7.111554989885978</v>
+        <v>4.255493652976995</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>85.59730556951661</v>
+        <v>96.49266198956654</v>
       </c>
       <c r="C8" t="n">
         <v>113.6515121553035</v>
       </c>
       <c r="D8" t="n">
-        <v>28.05420658578689</v>
+        <v>17.15885016573695</v>
       </c>
       <c r="E8" t="n">
-        <v>1.540554499237686</v>
+        <v>0.9076038784150882</v>
       </c>
       <c r="F8" t="n">
-        <v>5.648699830538182</v>
+        <v>3.32788088752199</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>84.29953903478676</v>
+        <v>95.74071599962393</v>
       </c>
       <c r="C9" t="n">
         <v>113.6515116632405</v>
       </c>
       <c r="D9" t="n">
-        <v>29.35197262845378</v>
+        <v>17.91079566361661</v>
       </c>
       <c r="E9" t="n">
-        <v>1.297766042666893</v>
+        <v>0.7519454978796603</v>
       </c>
       <c r="F9" t="n">
-        <v>4.758475489778609</v>
+        <v>2.757133492225421</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>83.16036089482112</v>
+        <v>95.09152553839024</v>
       </c>
       <c r="C10" t="n">
         <v>113.6515112150991</v>
       </c>
       <c r="D10" t="n">
-        <v>30.491150320278</v>
+        <v>18.55998567670888</v>
       </c>
       <c r="E10" t="n">
-        <v>1.139177691824216</v>
+        <v>0.6491900130922659</v>
       </c>
       <c r="F10" t="n">
-        <v>4.176984870022125</v>
+        <v>2.380363381338308</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>82.13346294777209</v>
+        <v>94.51563907124761</v>
       </c>
       <c r="C11" t="n">
         <v>113.6515108069587</v>
       </c>
       <c r="D11" t="n">
-        <v>31.51804785918661</v>
+        <v>19.13587173571109</v>
       </c>
       <c r="E11" t="n">
-        <v>1.026897538908614</v>
+        <v>0.5758860590022152</v>
       </c>
       <c r="F11" t="n">
-        <v>3.76529097599825</v>
+        <v>2.111582216341456</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>81.1925951120171</v>
+        <v>93.99606889919356</v>
       </c>
       <c r="C12" t="n">
         <v>113.6515104352489</v>
       </c>
       <c r="D12" t="n">
-        <v>32.45891532323175</v>
+        <v>19.65544153605529</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9408674640451409</v>
+        <v>0.5195698003442004</v>
       </c>
       <c r="F12" t="n">
-        <v>3.449847368165516</v>
+        <v>1.905089267928735</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>80.32219375938546</v>
+        <v>93.5225087069894</v>
       </c>
       <c r="C13" t="n">
         <v>113.6515100967178</v>
       </c>
       <c r="D13" t="n">
-        <v>33.32931633733236</v>
+        <v>20.12900138972842</v>
       </c>
       <c r="E13" t="n">
-        <v>0.870401014100608</v>
+        <v>0.4735598536731231</v>
       </c>
       <c r="F13" t="n">
-        <v>3.191470385035563</v>
+        <v>1.736386130134785</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>79.51244249626194</v>
+        <v>93.08828004097299</v>
       </c>
       <c r="C14" t="n">
         <v>113.651509788404</v>
       </c>
       <c r="D14" t="n">
-        <v>34.13906729214209</v>
+        <v>20.56322974743104</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8097509548097293</v>
+        <v>0.4342283577026222</v>
       </c>
       <c r="F14" t="n">
-        <v>2.96908683430234</v>
+        <v>1.592170644909615</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>78.75666228567486</v>
+        <v>92.68871438410744</v>
       </c>
       <c r="C15" t="n">
         <v>113.6515095076103</v>
       </c>
       <c r="D15" t="n">
-        <v>34.89484722193544</v>
+        <v>20.96279512350286</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7557799297933485</v>
+        <v>0.3995653760718199</v>
       </c>
       <c r="F15" t="n">
-        <v>2.771193075908945</v>
+        <v>1.465073045596673</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>78.04992816888775</v>
+        <v>92.32029210044084</v>
       </c>
       <c r="C16" t="n">
         <v>113.6515092518802</v>
       </c>
       <c r="D16" t="n">
-        <v>35.60158108299247</v>
+        <v>21.33121715143938</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7067338610570317</v>
+        <v>0.3684220279365178</v>
       </c>
       <c r="F16" t="n">
-        <v>2.59135749054245</v>
+        <v>1.350880769100565</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>77.38833282397593</v>
+        <v>91.98018108768493</v>
       </c>
       <c r="C17" t="n">
         <v>113.6515090189766</v>
       </c>
       <c r="D17" t="n">
-        <v>36.26317619500064</v>
+        <v>21.67132793129164</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6615951120081718</v>
+        <v>0.3401107798522673</v>
       </c>
       <c r="F17" t="n">
-        <v>2.425848744029963</v>
+        <v>1.247072859458314</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>76.76859166823897</v>
+        <v>91.66598688465551</v>
       </c>
       <c r="C18" t="n">
         <v>113.6515088068619</v>
       </c>
       <c r="D18" t="n">
-        <v>36.88291713862294</v>
+        <v>21.9855219222064</v>
       </c>
       <c r="E18" t="n">
-        <v>0.619740943622304</v>
+        <v>0.3141939909147595</v>
       </c>
       <c r="F18" t="n">
-        <v>2.272383459948448</v>
+        <v>1.152044633354118</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>76.1878285792374</v>
+        <v>91.37561490127943</v>
       </c>
       <c r="C19" t="n">
         <v>113.6515086136806</v>
       </c>
       <c r="D19" t="n">
-        <v>37.46368003444316</v>
+        <v>22.27589371240113</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5807628958202145</v>
+        <v>0.290371790194726</v>
       </c>
       <c r="F19" t="n">
-        <v>2.129463951340786</v>
+        <v>1.064696564047329</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>75.64345734458429</v>
+        <v>91.10719231242433</v>
       </c>
       <c r="C20" t="n">
         <v>113.6515084377425</v>
       </c>
       <c r="D20" t="n">
-        <v>38.00805109315826</v>
+        <v>22.54431612531822</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5443710587151003</v>
+        <v>0.26842241291709</v>
       </c>
       <c r="F20" t="n">
-        <v>1.996027215288701</v>
+        <v>0.9842155140293301</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>75.13311402897651</v>
+        <v>90.85902188566726</v>
       </c>
       <c r="C21" t="n">
         <v>113.6515082775087</v>
       </c>
       <c r="D21" t="n">
-        <v>38.51839424853223</v>
+        <v>22.79248639184148</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5103431553739739</v>
+        <v>0.2481702665232604</v>
       </c>
       <c r="F21" t="n">
-        <v>1.871258236371238</v>
+        <v>0.9099576439186213</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>74.65461658378754</v>
+        <v>90.62955306657531</v>
       </c>
       <c r="C22" t="n">
         <v>113.6515081315774</v>
       </c>
       <c r="D22" t="n">
-        <v>38.99689154778987</v>
+        <v>23.0219550650021</v>
       </c>
       <c r="E22" t="n">
-        <v>0.47849729925764</v>
+        <v>0.2294686731606248</v>
       </c>
       <c r="F22" t="n">
-        <v>1.754490097278013</v>
+        <v>0.8413851349222909</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>74.20593917661655</v>
+        <v>90.41736253883199</v>
       </c>
       <c r="C23" t="n">
         <v>113.6515079986719</v>
       </c>
       <c r="D23" t="n">
-        <v>39.44556882205534</v>
+        <v>23.23414545983989</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4486772742654637</v>
+        <v>0.2121903948377906</v>
       </c>
       <c r="F23" t="n">
-        <v>1.645150005640033</v>
+        <v>0.7780314477385654</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>73.78519460460738</v>
+        <v>90.22114011918785</v>
       </c>
       <c r="C24" t="n">
         <v>113.6515078776296</v>
       </c>
       <c r="D24" t="n">
-        <v>39.86631327302217</v>
+        <v>23.4303677584417</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4207444509668363</v>
+        <v>0.1962222986018105</v>
       </c>
       <c r="F24" t="n">
-        <v>1.542729653545067</v>
+        <v>0.7194817615399719</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>73.39062126394063</v>
+        <v>90.03967777335124</v>
       </c>
       <c r="C25" t="n">
         <v>113.6515077673915</v>
       </c>
       <c r="D25" t="n">
-        <v>40.26088650345082</v>
+        <v>23.61182999404021</v>
       </c>
       <c r="E25" t="n">
-        <v>0.394573230428648</v>
+        <v>0.1814622355985023</v>
       </c>
       <c r="F25" t="n">
-        <v>1.446768511571709</v>
+        <v>0.6653615305278416</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>73.02057279067559</v>
+        <v>89.87186055854202</v>
       </c>
       <c r="C26" t="n">
         <v>113.6515076669932</v>
       </c>
       <c r="D26" t="n">
-        <v>40.63093487631758</v>
+        <v>23.77964710845114</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3700483728667621</v>
+        <v>0.1678171144109371</v>
       </c>
       <c r="F26" t="n">
-        <v>1.356844033844794</v>
+        <v>0.6153294195067692</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>72.67350935720016</v>
+        <v>89.71665883911531</v>
       </c>
       <c r="C27" t="n">
         <v>113.6515075755564</v>
       </c>
       <c r="D27" t="n">
-        <v>40.97799821835625</v>
+        <v>23.9348487364411</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3470633420386662</v>
+        <v>0.1552016279899533</v>
       </c>
       <c r="F27" t="n">
-        <v>1.272565587475109</v>
+        <v>0.569072635963162</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>72.34799006911334</v>
+        <v>89.57312140922339</v>
       </c>
       <c r="C28" t="n">
         <v>113.6515074922813</v>
       </c>
       <c r="D28" t="n">
-        <v>41.30351742316793</v>
+        <v>24.07838608305788</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3255192048116839</v>
+        <v>0.1435373466167817</v>
       </c>
       <c r="F28" t="n">
-        <v>1.193570417642841</v>
+        <v>0.5263036042615331</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>72.04266615213923</v>
+        <v>89.44036931017179</v>
       </c>
       <c r="C29" t="n">
         <v>113.6515074164393</v>
       </c>
       <c r="D29" t="n">
-        <v>41.60884126430003</v>
+        <v>24.21113810626747</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3053238411320933</v>
+        <v>0.1327520232095907</v>
       </c>
       <c r="F29" t="n">
-        <v>1.119520750817675</v>
+        <v>0.4867574184351658</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>71.75627474937944</v>
+        <v>89.3175902129353</v>
       </c>
       <c r="C30" t="n">
         <v>113.6515073473669</v>
       </c>
       <c r="D30" t="n">
-        <v>41.8952325979875</v>
+        <v>24.33391713443164</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2863913336874759</v>
+        <v>0.1227790281641745</v>
       </c>
       <c r="F30" t="n">
-        <v>1.050101556854078</v>
+        <v>0.4501897699353066</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>71.48763321955734</v>
+        <v>89.20403328152209</v>
       </c>
       <c r="C31" t="n">
         <v>113.65150728446</v>
       </c>
       <c r="D31" t="n">
-        <v>42.16387406490267</v>
+        <v>24.44747400293792</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2686414669151702</v>
+        <v>0.1135568685062793</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9850187120222907</v>
+        <v>0.4163751845230242</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>71.23563386526331</v>
+        <v>89.09900445810275</v>
       </c>
       <c r="C32" t="n">
         <v>113.6515072271681</v>
       </c>
       <c r="D32" t="n">
-        <v>42.41587336190479</v>
+        <v>24.55250276906534</v>
       </c>
       <c r="E32" t="n">
-        <v>0.251999297002115</v>
+        <v>0.1050287661274183</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9239974223410883</v>
+        <v>0.3851054758005337</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>70.9992390415554</v>
+        <v>89.00186212536892</v>
       </c>
       <c r="C33" t="n">
         <v>113.6515071749901</v>
       </c>
       <c r="D33" t="n">
-        <v>42.65226813343469</v>
+        <v>24.64964504962117</v>
       </c>
       <c r="E33" t="n">
-        <v>0.236394771529902</v>
+        <v>0.09714228055582907</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8667808289429738</v>
+        <v>0.3561883620380399</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>70.77747660753573</v>
+        <v>88.91201311037739</v>
       </c>
       <c r="C34" t="n">
         <v>113.6515071274695</v>
       </c>
       <c r="D34" t="n">
-        <v>42.87403051993375</v>
+        <v>24.7394940170921</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2217623864990657</v>
+        <v>0.08984896747092819</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8131287504965741</v>
+        <v>0.32944621406007</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>70.56943569090021</v>
+        <v>88.82890899979128</v>
       </c>
       <c r="C35" t="n">
         <v>113.6515070841906</v>
       </c>
       <c r="D35" t="n">
-        <v>43.08207139329039</v>
+        <v>24.82259808439932</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2080408733566372</v>
+        <v>0.08310406730721809</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7628165356410032</v>
+        <v>0.3047149134597997</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>70.37426274017309</v>
+        <v>88.75204274033541</v>
       </c>
       <c r="C36" t="n">
         <v>113.6515070447747</v>
       </c>
       <c r="D36" t="n">
-        <v>43.27724430460162</v>
+        <v>24.89946430443931</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1951729113112322</v>
+        <v>0.07686622003998878</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7156340081411846</v>
+        <v>0.2818428068132922</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>70.19115784257298</v>
+        <v>88.68094550118742</v>
       </c>
       <c r="C37" t="n">
         <v>113.6515070088771</v>
       </c>
       <c r="D37" t="n">
-        <v>43.46034916630414</v>
+        <v>24.97056150768969</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1831048617025175</v>
+        <v>0.07109720325038893</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6713844929092309</v>
+        <v>0.2606897452514261</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>70.01937128784326</v>
+        <v>88.61518377732487</v>
       </c>
       <c r="C38" t="n">
         <v>113.6515069761837</v>
       </c>
       <c r="D38" t="n">
-        <v>43.63213568834045</v>
+        <v>25.03632319885884</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1717865220363137</v>
+        <v>0.06576169116914343</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6298839141331504</v>
+        <v>0.2411262009535259</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>69.85820036025905</v>
+        <v>88.55435671476502</v>
       </c>
       <c r="C39" t="n">
         <v>113.6515069464085</v>
       </c>
       <c r="D39" t="n">
-        <v>43.79330658614946</v>
+        <v>25.09715023164348</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1611708978090007</v>
+        <v>0.06082703278464408</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5909599586330027</v>
+        <v>0.2230324535436949</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>69.70698634258095</v>
+        <v>88.49809364028538</v>
       </c>
       <c r="C40" t="n">
         <v>113.6515069192911</v>
       </c>
       <c r="D40" t="n">
-        <v>43.94452057671012</v>
+        <v>25.15341327900569</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1512139905606631</v>
+        <v>0.05626304736220789</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5544512987224314</v>
+        <v>0.2062978403280956</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>69.56511171706549</v>
+        <v>88.44605177967352</v>
       </c>
       <c r="C41" t="n">
         <v>113.6515068945941</v>
       </c>
       <c r="D41" t="n">
-        <v>44.08639517752864</v>
+        <v>25.20545511492061</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1418746008185252</v>
+        <v>0.0520418359149204</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5202068696679257</v>
+        <v>0.1908200650213748</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>69.43199754982287</v>
+        <v>88.39791414986244</v>
       </c>
       <c r="C42" t="n">
         <v>113.6515068721017</v>
       </c>
       <c r="D42" t="n">
-        <v>44.21950932227882</v>
+        <v>25.25359272223925</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1331141447501807</v>
+        <v>0.04813760731863681</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4880851974173292</v>
+        <v>0.176504560168335</v>
       </c>
     </row>
   </sheetData>
